--- a/www/download/COUNTRY.FIN.rpO1.xlsx
+++ b/www/download/COUNTRY.FIN.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Finlândia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>0.733573431220508</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>0.772272322275964</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.871915557756043</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.89762575613992</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.938262378300011</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.08271976614765</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1.11656987699161</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>1.05752963905731</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.884017007086561</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.803923182182888</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.803793922960251</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>0.796431999450991</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.729660723656212</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.67990207486318</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948692920124</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.053</t>
+          <t>2.8675979120389</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.082</t>
+          <t>2.75836163123783</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.153</t>
+          <t>2.66151654736132</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>2.59052020336579</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.247</t>
+          <t>2.63609292661345</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.293</t>
+          <t>2.54260259931966</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>2.48365128097707</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.346</t>
+          <t>2.52788793065018</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.348</t>
+          <t>2.78050117938112</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>2.49797285647994</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>2.50337825718435</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.433</t>
+          <t>2.43234395975073</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2.32601852203402</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.541</t>
+          <t>2.22995401858683</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>2.19042850485076</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>3.9357353220025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>3.78659873030267</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.865</t>
+          <t>3.65755947414291</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>3.6109363681139</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.968</t>
+          <t>3.80600589141659</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>3.71929279815329</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.051</t>
+          <t>3.56772889076513</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>3.6476115973384</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.75183788929322</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.088</t>
+          <t>3.71138496709742</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>3.77013353067011</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.153</t>
+          <t>3.69379412087691</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.201</t>
+          <t>3.70523513269537</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.234</t>
+          <t>3.64660070952497</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>3.56695183050294</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3645.8</t>
+          <t>3.78532468142869</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3695.2</t>
+          <t>3.65899280446743</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3811.8</t>
+          <t>3.54995305841975</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3860.6</t>
+          <t>3.66797645143484</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3964.7</t>
+          <t>3.91500973482951</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4014.9</t>
+          <t>3.87239981681386</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4027.8</t>
+          <t>3.73022859790123</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4049.8</t>
+          <t>3.83074144811753</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4034.9</t>
+          <t>3.61299740761919</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4061.5</t>
+          <t>3.85979601930165</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4099.4</t>
+          <t>3.90923775863507</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4157.8</t>
+          <t>3.81713966465351</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>4242.2</t>
+          <t>3.62544797205678</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4292.752</t>
+          <t>3.43233979041224</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>4119.799</t>
+          <t>3.34905437804344</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>6807103392265.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2963.1</t>
+          <t>5954015337592.46</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3079.1</t>
+          <t>5805512163617.79</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3160.6</t>
+          <t>6675607106022.48</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3234.5</t>
+          <t>7212899134217.6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>7757598606241.74</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3338.8</t>
+          <t>8346560576273.53</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3372.6</t>
+          <t>8520206058527.93</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3374.3</t>
+          <t>9846767941282.6</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3397.5</t>
+          <t>9454165372174.77</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3436.3</t>
+          <t>8916673522832.49</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3485.8</t>
+          <t>8278660680606.09</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3563.4</t>
+          <t>7131151428785.18</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3620.7</t>
+          <t>5691513020705.38</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3434.5</t>
+          <t>4924339989942.08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>1162310104633.41</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>1032138170631.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>988818572921.833</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>1146748237548.99</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>1222764639735.58</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.74</t>
+          <t>1274189021598.1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.85</t>
+          <t>1406014575436.83</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>1471480764766.08</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.12</t>
+          <t>1719186531575.84</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>1625841783453.87</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>1521978518016.63</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>1374361164598.14</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>39.62</t>
+          <t>1190049742033.23</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>1017798233093.03</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>932547426770.837</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>40.27</t>
+          <t>975884019.235112</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40.87</t>
+          <t>867635186.559877</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41.49</t>
+          <t>877264181.96042</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>976130987.647325</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>1073689862.12816</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>1201638282.01849</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>43.21</t>
+          <t>1294498545.82388</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>1234675138.66513</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>1183396534.33153</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>973875502.408221</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>869273916.015552</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>733955898.923442</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>43.04</t>
+          <t>528227310.53239</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>368492330.736582</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>388893067.615407</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>170511.451989104</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>171580.089086761</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>164726.927221784</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>174082.067960813</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>175945.046252206</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22.63</t>
+          <t>163521.443943394</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>169755.44373943</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>184243.182629104</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21.89</t>
+          <t>225039.008024376</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>259257.720716662</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>272252.652948598</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>287666.397697278</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>331909.741431214</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>16.99</t>
+          <t>378177.762255925</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>355832.998797654</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>306024.786060198</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>300652.380588713</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>286995.239315165</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>299485.713067776</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>301632.640021365</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>28.54</t>
+          <t>286043.772806934</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>291014.527826246</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>310593.481526674</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>377157.218447889</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>30.36</t>
+          <t>435237.185736005</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>459498.168315724</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>494868.666090532</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>568472.465273957</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>604483.318460907</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>544505.68885294</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>29.07</t>
+          <t>29434.7894310522</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>26365.5260503027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.86</t>
+          <t>24099.328130321</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.67</t>
+          <t>23518.8618626669</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>22374.8318174798</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.15</t>
+          <t>20485.1236655733</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>21545.0830131354</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>22378.5344811173</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>26699.28266116</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>29702.3915195364</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>30476.6065741515</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>31487.5915397625</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>35722.9024123712</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>17.57</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.733573431220508</t>
+          <t>656042.278395559</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.772272322275964</t>
+          <t>573665.057042852</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.871915557756043</t>
+          <t>530083.935307083</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89762575613992</t>
+          <t>597202.498463178</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262378300011</t>
+          <t>621260.359585196</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976614765</t>
+          <t>632885.820095418</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987699161</t>
+          <t>685559.791036536</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963905731</t>
+          <t>708635.090183522</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017007086561</t>
+          <t>826492.251130155</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182182888</t>
+          <t>778473.44192189</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793922960251</t>
+          <t>718320.992078831</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999450991</t>
+          <t>638258.099009957</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660723656212</t>
+          <t>540587.690575645</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.67990207486318</t>
+          <t>455574.161001309</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948692920124</t>
+          <t>432355.429909053</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-179963795802.156</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-144952733858.006</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-104568588027.223</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-24433507045.0605</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>-9609351697.50935</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>-6870797013.72941</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-16518497758.4418</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>9917956975.19129</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-52520026435.7723</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>-61840921758.3067</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>-81936623759.7891</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>-64163408625.369</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>-5432395733.64725</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>25551806037.4847</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>-106766386180.889</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>-31421939017.332</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>-16494726460.3466</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>33297562007.0252</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>109084258954.483</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>105895844462.069</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>195140053935.862</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>128582724580.086</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>146558894705.098</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>132868154346.312</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>113358334052.118</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>108528278691.749</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>116886332141.99</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>175344092719.339</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>207709599482.927</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>25514372335.1743</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>-148541856784.824</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>-128458007397.66</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>-137866150034.248</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>-133517765999.544</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-115505196159.578</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>-202010850949.592</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>-145101222338.528</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>-136640937729.906</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>-185388180782.084</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>-175199255810.425</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>-190464902451.538</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-181049740767.359</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>-180776488452.986</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-182157793445.442</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-132280758516.064</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2940694.84315983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>2495146.33650013</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>2246113.2093416</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>2516890.9513868</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>2700699.44104578</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>2697331.60183182</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>2843180.4576854</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>2980612.69357021</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>3573793.73971379</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>3268592.56863453</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>3036467.13803177</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>2644022.8851692</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>2189650.01054952</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>1799406.31394256</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1671759.11681171</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>3038392.99620399</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2692238.64026691</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>2550030.46631767</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2919811.56052168</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.113</t>
+          <t>3112583.04572501</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>3237423.63012911</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>3518162.88697687</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>3644888.52841678</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>4272141.63100683</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>4096903.73083883</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>3809773.93657572</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>3407980.9274822</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>2900085.99519991</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.238</t>
+          <t>2440085.54676959</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>2311443.3078962</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>286.76</t>
+          <t>46602.1927758937</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>275.84</t>
+          <t>46729.9583041946</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>266.15</t>
+          <t>46493.8429920393</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>259.05</t>
+          <t>48793.8311815811</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>263.61</t>
+          <t>49564.3941345042</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>254.26</t>
+          <t>51553.402734727</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>248.37</t>
+          <t>50362.3725617934</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>252.79</t>
+          <t>53089.8310980472</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>278.05</t>
+          <t>61683.8070180424</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>249.8</t>
+          <t>73102.2887236213</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>250.34</t>
+          <t>79071.6106660618</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>243.23</t>
+          <t>91424.9950671943</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>232.6</t>
+          <t>109319.492699324</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>123398.018391332</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>219.04</t>
+          <t>87225.8247802957</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>393.57</t>
+          <t>1595807381095.82</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>378.66</t>
+          <t>1418897188483.17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>365.76</t>
+          <t>1422023229575.01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>361.09</t>
+          <t>1610144644989.72</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>380.6</t>
+          <t>1739558157886.59</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>371.93</t>
+          <t>1982242862645.13</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>356.77</t>
+          <t>2109120873417.84</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>364.76</t>
+          <t>2126072869296.48</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>375.18</t>
+          <t>2368702852003.7</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>371.14</t>
+          <t>2310130196648.42</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>377.01</t>
+          <t>2178169652288.95</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>369.38</t>
+          <t>2116849321438.34</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>370.52</t>
+          <t>1812766698454.61</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>364.66</t>
+          <t>1416025418436.64</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>356.7</t>
+          <t>1070514606978.96</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>378.53</t>
+          <t>35247.6713112743</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>365.9</t>
+          <t>36045.8139090302</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>35691.4596345649</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>366.8</t>
+          <t>36485.122976794</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>391.5</t>
+          <t>36014.1148455671</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>387.24</t>
+          <t>38668.4687917521</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>373.02</t>
+          <t>37248.947742656</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>383.07</t>
+          <t>39039.1196999104</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>361.3</t>
+          <t>48458.4510333796</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>385.98</t>
+          <t>58277.7921699471</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>390.92</t>
+          <t>68175.8269779987</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>381.71</t>
+          <t>78162.4060985394</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>362.54</t>
+          <t>92552.1690788116</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>343.23</t>
+          <t>108837.962921108</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>334.91</t>
+          <t>79860.246117199</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6236909.303</t>
+          <t>1001438251106.42</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5604702.401</t>
+          <t>926231170926.019</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5489960.591</t>
+          <t>957350293173.504</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6402270.809</t>
+          <t>1124118513338.38</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6994596.62</t>
+          <t>1182826520167.46</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7424707.353</t>
+          <t>1389063230572.17</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8176914.182</t>
+          <t>1450929472460.74</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8551637.465</t>
+          <t>1473145249612.2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>10029279.693</t>
+          <t>1728493354990.88</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9655992.403</t>
+          <t>1707943681233.9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9102311.889</t>
+          <t>1743168114510.85</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8292299.193</t>
+          <t>1686293484240</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>7209903.793</t>
+          <t>1466276946685.78</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6199809.417</t>
+          <t>1222672918930.77</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>5705529.185</t>
+          <t>854783188243.437</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5210029.054</t>
+          <t>11354.5214646194</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4489267.289</t>
+          <t>10684.1443951645</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4189899.581</t>
+          <t>10802.3833574745</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4832934.005</t>
+          <t>12308.7082047871</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5315516.64</t>
+          <t>13550.2792889371</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5430537.714</t>
+          <t>12884.9339429749</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5831078.801</t>
+          <t>13113.4248191374</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6189242.258</t>
+          <t>14050.7113981367</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7433848.358</t>
+          <t>13225.3559846628</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6826455.58</t>
+          <t>14824.4965536741</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6433666.572</t>
+          <t>10895.7836880631</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5693374.479</t>
+          <t>13262.5889686549</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>4820295.533</t>
+          <t>16767.3236205123</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>4020053.646</t>
+          <t>14560.0554702245</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3605817.239</t>
+          <t>7365.57866309673</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6807103.392</t>
+          <t>594369129989.403</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5954015.338</t>
+          <t>492666017557.154</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5805512.164</t>
+          <t>464672936401.504</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>6675607.106</t>
+          <t>486026131651.341</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7212899.134</t>
+          <t>556731637719.134</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7757598.606</t>
+          <t>593179632072.968</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8346560.576</t>
+          <t>658191400957.096</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8520206.059</t>
+          <t>652927619684.281</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>9846767.941</t>
+          <t>640209497012.82</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>9454165.372</t>
+          <t>602186515414.52</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8916673.523</t>
+          <t>435001537778.091</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8278660.681</t>
+          <t>430555837198.342</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>7131151.429</t>
+          <t>346489751768.833</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5691513.021</t>
+          <t>193352499505.873</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>4924339.99</t>
+          <t>215731418735.519</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>64200.79909</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>61759.30231</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>58503.37221</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>62327.75749</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>61869.68785</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>58261.61286</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>59201.8479</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>63413.82581</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>76507.57744</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>87157.58111</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>90008.14496</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>96229.18212</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>115291.93935</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>124463.51194</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>103229.14414</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3792794.362</t>
+          <t>0.0189138531738914</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3397912.5</t>
+          <t>0.0225221645238238</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3332195.272</t>
+          <t>0.0299252922407378</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3880330.31</t>
+          <t>0.0403953505507245</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4207349.283</t>
+          <t>0.0432499521060523</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4434753.86</t>
+          <t>0.0505733244248037</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4868740.076</t>
+          <t>0.0485089947592811</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5054162.351</t>
+          <t>0.0521776595090084</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>5875286.966</t>
+          <t>0.0489114758100198</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5631562.389</t>
+          <t>0.0533423397070572</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>5283128.834</t>
+          <t>0.0487240812627278</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4812372.775</t>
+          <t>0.0508234311114752</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4163611.734</t>
+          <t>0.0604489780828278</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3560732.931</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>3218042.899</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>64780.1545720892</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>64117.2790306618</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>59836.0697050603</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>62504.8914512194</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>62601.8923411265</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>57618.7875727284</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>59520.6814993623</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>64725.3726908649</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>79674.9373851652</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>91179.109613634</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>95969.8720259783</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>101251.582030597</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>117111.963314036</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>133967.8212127</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>126339.07733036</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1162310.105</t>
+          <t>76548.6526088396</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1032138.171</t>
+          <t>75928.4406545897</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>988818.573</t>
+          <t>70740.1372455899</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1146748.238</t>
+          <t>73138.9017173403</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1222764.64</t>
+          <t>73475.8848258086</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1274189.022</t>
+          <t>67381.129906586</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1406014.575</t>
+          <t>69040.5710335755</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1471480.765</t>
+          <t>74896.1260440397</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1719186.532</t>
+          <t>91922.7636145912</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1625841.783</t>
+          <t>105216.960221896</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1521978.518</t>
+          <t>110653.750386334</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1374361.165</t>
+          <t>116859.797080634</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1190049.742</t>
+          <t>134984.0403848</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1017798.233</t>
+          <t>154720.822196622</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>932547.427</t>
+          <t>145394.444269938</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>434990.525963539</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>412643.00441802</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>381606.223665989</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>388762.780515372</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>389772.201027538</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>364000.321458247</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>383057.173530358</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>407346.842208847</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>492317.157588525</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>560784.573433505</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>592896.670205935</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>630188.406590516</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>734524.414821197</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>975.884</t>
+          <t>76548.6526088396</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>867.635</t>
+          <t>80020.2330856799</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>877.264</t>
+          <t>83389.1472750524</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>976.131</t>
+          <t>85332.2044840451</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1073.69</t>
+          <t>88639.7472275423</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1201.638</t>
+          <t>91440.1570608733</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1294.499</t>
+          <t>93124.6963278419</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1234.675</t>
+          <t>94367.3206985582</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1183.397</t>
+          <t>96812.5996990925</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>973.876</t>
+          <t>99869.768988331</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>869.274</t>
+          <t>104735.859668845</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>733.956</t>
+          <t>109401.97646161</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>528.227</t>
+          <t>111988.208159261</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>368.492</t>
+          <t>117681.767594062</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>388.893</t>
+          <t>117869.305008202</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>64780.1545720892</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>67653.4194594542</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>70695.8077077831</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>73108.0423646639</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>76078.7651134119</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>78744.0237285374</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80912.5039189161</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>82068.4674150358</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>84607.7513643575</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>87367.4140641673</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>91812.1413447876</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>95751.0737689078</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>98755.6331667538</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>103743.762731314</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>103924.800250466</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>37662.1363711604</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>35659.1396854103</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>35519.0058944101</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>39223.0706626597</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>39232.4608441914</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>38893.830013414</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>40126.8014364245</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>43632.9393159603</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>50779.2414054088</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>59615.9527381036</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>59364.9521136662</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>63515.9286093659</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>80124.1526651996</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>82819.2677833777</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>62215.9487400622</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5210029053626.28</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4489267288631.03</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>4189899580705.81</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4832934004852.93</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>5315516639866.31</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5430537713968</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5831078800667</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6189242258198.54</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>7433848357978.66</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6826455579593.23</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6433666572061.72</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5693374478634.85</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4820295533223.71</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>4020053645979.07</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3605817239051.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>6236909303307.93</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5604702401307.66</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5489960590935.31</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>6402270808755.88</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>6994596620353.25</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>7424707353338.1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8176914181911.65</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8551637465371.46</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>10029279692951.6</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9655992403214.04</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9102311889266.71</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8292299192749.7</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>7209903792666.51</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6199809416917.8</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5705529184872.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3792794362175.59</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3397912499637.15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3332195272449.31</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>3880330310271.93</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4207349283196.02</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4434753860144.71</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4868740075991.36</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>5054162351260.23</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>5875286966192.92</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5631562389421.22</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5283128833714.22</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4812372774703.78</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4163611733937.31</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>3560732930564.77</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>3218042899444.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2052700</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2081800</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2152900</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2192700</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2247200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2293400</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2324200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2346200</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2347600</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2356900</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2389200</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2433200</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2486100</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2540816.41732835</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2468383.78660693</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1771700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1799200</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1865400</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1920200</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1968200</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2013300</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2050900</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2076500</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2080100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2088500</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2118800</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2153300</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2201400</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2234100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>2156900</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3645800000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3695200000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3811800000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3860600000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3964700000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>4014900000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>4027800000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>4049800000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4034900000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>4061500000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>4099400000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>4157800000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>4242200000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4292752281.33335</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>4119798894.31217</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2.929e+09</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2963100000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3079100000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3160600000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3234500000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3.295e+09</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3338800000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3372600000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>3374300000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>3397500000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3436300000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3485800000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3563400000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3620700000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3434500000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.318785191966435</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.325242969869431</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.328975048732311</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.33456523972237</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.345601204103223</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.347387444600473</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.348525926203091</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.353739437247561</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.341164951748857</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.37058464701845</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.374091954269727</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.379122833708382</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.396175341819239</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.403158238395283</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.420199510053656</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.402729758764687</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.408709118495148</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.414861778032466</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.418897551821378</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.419807628286951</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.426340817820327</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.432089115527316</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.435300420804858</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.439944509231172</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.442742323919603</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.442416584481061</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.444235964690608</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.430430710493054</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.42698941120088</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.422997689638566</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.278485049268878</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.26604791163542</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.256163173235223</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.246537208456252</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.234591167609826</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.2262717375792</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.219384958269592</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.210960141947581</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.218890539019971</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.186673029061948</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.183491461249212</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.176641201601009</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.173393947687707</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.169852350403836</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.156802800307778</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.273962792452623</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.280187048772489</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.283290645672041</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.282732007640922</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.285006629270886</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.285377458913775</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.288824914960104</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.292661282276355</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.297260406877777</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.303567149908334</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.304474725809539</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.307989294577137</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.316946499155567</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.320349632916784</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.337259191383188</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.435316951886601</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.441566304892616</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.448133256416424</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.450608738153833</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.456051366651535</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.463080981079406</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.467042078216123</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.471163259919086</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.47676111747414</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.485667845821841</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.487876600547858</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.491498400324855</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.489432125542819</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.490929019346309</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.487053716418833</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.290720255660776</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.278246646334896</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.268576097911535</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.266659254205245</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.258942004077579</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.251541560006819</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.244133006823773</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.23617545780456</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.225978475648083</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.210765004269826</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.207648673642603</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.200512305098008</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.193621375301614</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.188721347736907</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.175687092197979</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>239854.6551</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>237907.01329</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>229104.75534</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>240112.3178</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>241264.06981</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>235411.79038</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>233919.97869</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>252336.19007</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>306651.34026</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>357016.69779</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>377278.29372</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>413452.74915</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>487841.7983</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>552253.05822</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>469673.77601</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>114210.78898</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>111587.58034</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>106259.14314</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>112361.97238</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>112708.34567</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>106274.95992</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>109167.37247</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>118529.06536</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>142702.00502</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>164832.91296</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>170018.7025</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>180375.72569</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>215108.19305</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>237540.08998</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>207610.39301</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>319097.493521892</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>324084.115838911</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>331309.229914356</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>340537.675261471</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>349979.093422943</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>359899.739289555</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>369274.772732724</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>377672.067190042</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>386600.001068428</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>395858.934852572</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>405924.105201978</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>417104.284403962</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>431105.275249461</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
